--- a/results/importance_variables.xlsx
+++ b/results/importance_variables.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,16 +413,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Importance</t>
         </is>
@@ -443,21 +431,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>statut_prevu</t>
+          <t>jour_semaine_num</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6167850390925516</v>
+        <v>663</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>priorite_recommandee</t>
+          <t>charge_precollecteur</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2261148840519681</v>
+        <v>525</v>
       </c>
     </row>
     <row r="4">
@@ -467,87 +455,87 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1123203930326198</v>
+        <v>407</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>charge_precollecteur</t>
+          <t>delta_fillRate_24h</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02381635571707856</v>
+        <v>385</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>risque_debordement</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005171465796639916</v>
+        <v>345</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>jour_semaine_num</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.003369947831922885</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rendement_remplissage</t>
+          <t>risque_debordement</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002934368153355489</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>delta_fillRate_24h</t>
+          <t>densite_population_hab_km2</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002860187295749893</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>rendement_remplissage</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0009666162265525621</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>is_weekend</t>
+          <t>indice_saturation</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0008513434408705203</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>poids_kg</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0007472745774859353</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13">
@@ -557,7 +545,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0006354736342523717</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14">
@@ -567,357 +555,337 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0006320341669327827</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>densite_population_hab_km2</t>
+          <t>temperature_celsius</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0005917892604052118</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>indice_saturation</t>
+          <t>indice_meteo</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.000501194402695747</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>nb_precollecteurs_dispo</t>
+          <t>humidite_pct</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.0004257975437231843</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>quartier_7</t>
+          <t>fillRate_t_minus_2</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.0001999563831686675</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>poids_kg</t>
+          <t>indice_priorite</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.0001538683127824783</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>fillRate_t_minus_1</t>
+          <t>nb_precollecteurs_dispo</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.0001370399444720367</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>fillRate_t_minus_2</t>
+          <t>fillRate_t_minus_1</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.0001082207510604239</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>arrondissement_1</t>
+          <t>rolling_mean_3d</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>9.939508791274515e-05</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>quartier_6</t>
+          <t>jours_depuis_derniere_collecte</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9.705204691238693e-05</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>arrondissement_2</t>
+          <t>is_jour_marche</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9.690497882902797e-05</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>is_jour_marche</t>
+          <t>quartier_6</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6.827207914420081e-05</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>quartier_8</t>
+          <t>arrondissement_1</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.649775797808331e-05</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>quartier_14</t>
+          <t>ratio_plaintes</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4.292245335099545e-05</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>jours_depuis_derniere_collecte</t>
+          <t>quartier_12</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.62955446000657e-05</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>quartier_12</t>
+          <t>quartier_11</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3.21009192178505e-05</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>rolling_mean_3d</t>
+          <t>arrondissement_4</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.031680468157595e-05</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>quartier_10</t>
+          <t>quartier_13</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.707500393222104e-05</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>arrondissement_3</t>
+          <t>quartier_1</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.626802747289187e-05</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>quartier_11</t>
+          <t>nb_signalements_citoyens</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.524598741440827e-05</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>quartier_5</t>
+          <t>quartier_4</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.359292512901858e-05</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>indice_meteo</t>
+          <t>is_weekend</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.315917326643316e-05</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>quartier_13</t>
+          <t>quartier_2</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>8.505298945470713e-06</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>temperature_celsius</t>
+          <t>quartier_7</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>6.518406255799849e-06</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>arrondissement_4</t>
+          <t>arrondissement_2</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5.434808096059887e-06</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>humidite_pct</t>
+          <t>quartier_8</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.193080572718364e-06</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>nb_plaintes</t>
+          <t>quartier_5</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>nb_signalements_citoyens</t>
+          <t>pression_citoyenne</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>quartier_4</t>
+          <t>quartier_3</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>quartier_1</t>
+          <t>arrondissement_3</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quartier_2</t>
+          <t>quartier_9</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>quartier_3</t>
+          <t>nb_plaintes</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>quartier_9</t>
+          <t>quartier_14</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ratio_plaintes</t>
+          <t>quartier_10</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>pression_citoyenne</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>indice_priorite</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
